--- a/backend/data/Data Sản Phẩm EXE/Kem chống nắng (1).xlsx
+++ b/backend/data/Data Sản Phẩm EXE/Kem chống nắng (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EXE101_App\backend\data\Data Sản Phẩm EXE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EA6B80-B976-49E7-9F3C-880A4ECE5CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93ADB34-7D95-4CED-A6BC-D91E888E693C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="240">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Link sản phẩm</t>
   </si>
   <si>
-    <t xml:space="preserve">Link ảnh </t>
-  </si>
-  <si>
     <t>Kem dưỡng ẩm chống nắng ban ngày Hada Labo Koi-Gokujyun UV White Gel SPF50+ PA++++ 90g</t>
   </si>
   <si>
@@ -48,88 +45,36 @@
     <t>Kem dưỡng ẩm chống nắng ban ngày Hada Labo Koi-Gokujyun UV White Gel SPF50+ PA++++ 90g | Shopee Việt Nam</t>
   </si>
   <si>
-    <t>https://ibb.co/MDJHt5m5</t>
-  </si>
-  <si>
     <t>Kem Chống Nắng Nâng Tone Vật Lý Tone Up SPF50+ PA+++ Tone Up Cho Mẹ Và Bé Cỏ Mềm 60gr | Shopee Việt Nam</t>
   </si>
   <si>
     <t>Cỏ mềm</t>
   </si>
   <si>
-    <t>https://ibb.co/39DJcvQt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kem Chống Nắng Nâng Tone Mịn Đẹp Thấm Nhanh Cho Mọi Loại Da Hây Hây SPF 40, PA ++ Cỏ Mềm 60g </t>
   </si>
   <si>
     <t>Kem Chống Nắng Nâng Tone Mịn Đẹp Thấm Nhanh Cho Mọi Loại Da Hây Hây SPF 40, PA ++ Cỏ Mềm 60g | Shopee Việt Nam</t>
   </si>
   <si>
-    <t>https://ibb.co/xtVt9NKm</t>
-  </si>
-  <si>
     <t>Sữa Chống Nắng Kiềm Dầu Ngừa Mụn Nâng Tone Rau Má Cho Da Dầu Mụn SPF 50+ PA++++ Cỏ Mềm 60gr</t>
   </si>
   <si>
     <t>Sữa Chống Nắng Kiềm Dầu Ngừa Mụn Nâng Tone Rau Má Cho Da Dầu Mụn SPF 50+ PA++++ Cỏ Mềm 60gr | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/27pWvkSG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Sữa Chống Nắng Nâng Tone Dưỡng Sáng Da Sơ Ri Vitamin C SPF 50+ PA++++ Cỏ Mềm 60gr </t>
   </si>
   <si>
     <t>Sữa Chống Nắng Nâng Tone Dưỡng Sáng Da Sơ Ri Vitamin C SPF 50+ PA++++ Cỏ Mềm 60gr | Shopee Việt Nam</t>
   </si>
   <si>
-    <t>https://ibb.co/4xmvxhV</t>
-  </si>
-  <si>
     <t>[SVIP] Kem Chống Nắng Sâm 1700 SPF50+ PA++++ Ngừa Lão Hoá Bảo Vệ Dưỡng Ẩm Da Cỏ Mềm 60g</t>
   </si>
   <si>
     <t>[SVIP] Kem Chống Nắng Sâm 1700 SPF50+ PA++++ Ngừa Lão Hoá Bảo Vệ Dưỡng Ẩm Da Cỏ Mềm 60g | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/qLXQQ9CD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng bí đao quang phổ rộng SPF 50 +, PA ++++ Cocoon 50ml </t>
   </si>
   <si>
@@ -139,61 +84,18 @@
     <t>Kem chống nắng bí đao quang phổ rộng SPF 50 +, PA ++++ Cocoon 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/GbzSD5f</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">MINI SIZE-Sữa chống nắng bí đao - Ráo mịn tự nhiên SPF 50+, UVA-PF 62.6 Cocooon 15ml </t>
   </si>
   <si>
     <t>MINI SIZE-Sữa chống nắng bí đao - Ráo mịn tự nhiên SPF 50+, UVA-PF 62.6 Cocooon 15ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/CK2xpRHp </t>
-  </si>
-  <si>
     <t xml:space="preserve">Sữa Chống Nắng Vô Cơ Sen Hậu Giang - Tone up Pink Cocoon 15ml </t>
   </si>
   <si>
     <t>Sữa Chống Nắng Vô Cơ Sen Hậu Giang - Tone up Pink Cocoon 15ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/PzYJ8HHH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng nâng tone cho da dầu La Roche-Posay Anthelios XL SPF50+ PA++++ 50ml </t>
   </si>
   <si>
@@ -203,130 +105,30 @@
     <t>[PHIÊN BẢN NÂNG TONE] Kem chống nắng nâng tone cho da dầu La Roche-Posay Anthelios XL SPF50+ PA++++ 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/v6j57Nd3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Sữa chống nắng chống tia UVA dài La Roche-Posay Anthelios UV Mune 400 </t>
   </si>
   <si>
     <t>Sữa chống nắng chống tia UVA dài La Roche-Posay Anthelios UV Mune 400 | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/8LBRGWYk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Chống nắng dạng Serum mỏng nhẹ kiềm dầu 16H, cấp ẩm 24H &amp; chống bụi mịn La Roche-Posay Anthelios UVAIR SPF50+ 50ml </t>
   </si>
   <si>
     <t>[MỚI] Chống nắng dạng Serum mỏng nhẹ kiềm dầu 16H, cấp ẩm 24H &amp; chống bụi mịn La Roche-Posay Anthelios UVAIR SPF50+ 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/tTcHpjYY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng nâng tone sáng hồng rạng rỡ cho da khô, xỉn màu Anthelios UVIDEA Rosy+ SPF50+, PA++++ </t>
   </si>
   <si>
     <t>Kem chống nắng nâng tone sáng hồng rạng rỡ cho da khô, xỉn màu Anthelios UVIDEA Rosy+ SPF50+, PA++++ | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/tTDc8Gy5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[PHIÊN BẢN DƯỠNG SÁNG] Sữa chống nắng dưỡng sáng Anthelios UVMUNE 400+ Anti-Dark Spots Fluid 50ml </t>
   </si>
   <si>
     <t>[PHIÊN BẢN DƯỠNG SÁNG] Sữa chống nắng dưỡng sáng Anthelios UVMUNE 400+ Anti-Dark Spots Fluid 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/NdgLKdgD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Round Lab Birch Juice Sunscreen 50ml bảo vệ da quang phổ rộng</t>
   </si>
   <si>
@@ -336,156 +138,36 @@
     <t>Kem chống nắng Round Lab Birch Juice Sunscreen 50ml bảo vệ da quang phổ rộng | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/Swg2CvsJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng Round Lab Birch Juice 50ml Sunscreen bảo vệ da </t>
   </si>
   <si>
     <t>Kem chống nắng Round Lab Birch Juice 50ml Sunscreen bảo vệ da | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/q3X8VJ6C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng hóa học Round Lab 1025 Dokdo Sunscreen 50ml dành cho da nhạy cảm </t>
   </si>
   <si>
     <t>Kem chống nắng hóa học Round Lab 1025 Dokdo Sunscreen 50ml dành cho da nhạy cảm | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/0yWM3qJV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem Chống Nắng Round Lab Birch Juice Moisturizing Tone-up Sunscreen 50ml Nâng Tone Trắng Hồng Tự Nhiên</t>
   </si>
   <si>
     <t>Kem Chống Nắng Round Lab Birch Juice Moisturizing Tone-up Sunscreen 50ml Nâng Tone Trắng Hồng Tự Nhiên | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/PvnTfc7k</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[LIVE ROUND LAB] Kem chống nắng Round Lab Birch Juice 50ml bảo vệ da quang phổ rộng </t>
   </si>
   <si>
     <t>[LIVE ROUND LAB] Kem chống nắng Round Lab Birch Juice 50ml bảo vệ da quang phổ rộng | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/DHCWfTjb</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Sáp chống nắng Round Lab Birch Juice Moisturizing Sun Stick 19g Phù Hợp Với Mọi Loại Da</t>
   </si>
   <si>
     <t>Sáp chống nắng Round Lab Birch Juice Moisturizing Sun Stick 19g Phù Hợp Với Mọi Loại Da | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/RTmz0hvr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Dear Klairs] Kem Nền Chống Nắng Dưỡng Da 2in1 SPF40 PA + + + 40 g [Natural/Ivory] </t>
   </si>
   <si>
@@ -495,35 +177,12 @@
     <t>[Dear Klairs] Kem Nền Chống Nắng Dưỡng Da 2in1 SPF40 PA + + + 40 g [Natural/Ivory] | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/6RVRvjY9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[MCN LIVE] [Dear Klairs] Kem Nền Chống Nắng Dưỡng Da 2in1 SPF40 PA + + + 40 g [Natural/Ivory] </t>
   </si>
   <si>
     <t>[MCN LIVE] [Dear Klairs] Kem Nền Chống Nắng Dưỡng Da 2in1 SPF40 PA + + + 40 g [Natural/Ivory] | Shopee Việt Nam</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/6RVRvjY  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Sữa chống nắng Bioderma phổ rộng ráo mịn, bảo vệ da toàn diện Photoderm XDefense Ultra-fluid SPF50+ 40ml </t>
   </si>
   <si>
@@ -533,52 +192,12 @@
     <t>Sữa chống nắng Bioderma phổ rộng ráo mịn, bảo vệ da toàn diện Photoderm XDefense Ultra-fluid SPF50+ 40ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/s9SS3gR5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Chống nắng dành cho da mụn Bioderma Photoderm Akn Mat Spf30 - 40ml </t>
   </si>
   <si>
     <t>Chống nắng dành cho da mụn Bioderma Photoderm Akn Mat Spf30 - 40ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/H1g7Lqy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem Chống Nắng Garnier Phổ Rộng Kiềm Dầu Đến 12H &amp; Hỗ Trợ Giảm Mụn Spf 50+PA++++ 30ML </t>
   </si>
   <si>
@@ -588,44 +207,18 @@
     <t>Kem Chống Nắng Garnier Phổ Rộng Kiềm Dầu Đến 12H &amp; Hỗ Trợ Giảm Mụn Spf 50+PA++++ 30ML | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/XfZCZ966</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">MỚI! Kem chống nắng mát da Watergel SPF50+ PA++++ - Garnier Super UV Cooling Watergel 30ml &amp; 60ml </t>
   </si>
   <si>
     <t>MỚI! Kem chống nắng mát da Watergel SPF50+ PA++++ - Garnier Super UV Cooling Watergel 30ml &amp; 60ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <t>https://ibb.co/SXN5YQYG</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng Garnier phổ rộng bảo vệ mạnh mẽ dễ chịu trên da SPF 50+ | PA++++ 30ML </t>
   </si>
   <si>
     <t>Kem chống nắng Garnier phổ rộng bảo vệ mạnh mẽ dễ chịu trên da SPF 50+ | PA++++ 30ML | Shopee Việt Nam</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/4ZK1NpfQ </t>
-  </si>
-  <si>
     <t xml:space="preserve">Chống nắng cơ thể Vaseline 50x bảo vệ da với SPF 50+ PA++++ giúp da sáng hơn gấp 2X 300ml </t>
   </si>
   <si>
@@ -635,87 +228,24 @@
     <t>Chống nắng cơ thể Vaseline 50x bảo vệ da với SPF 50+ PA++++ giúp da sáng hơn gấp 2X 300ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/9mjbB8J5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Serum chống nắng Vaseline GLUTA HYA SPF50 260ml/150ml </t>
   </si>
   <si>
     <t>Serum chống nắng Vaseline GLUTA HYA SPF50 260ml/150ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/9mjbB8J  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Serum chống nắng dưỡng thể hương tươi mát Vaseline Glow Defense SPF50+ PA++++ 260ML/150ML </t>
   </si>
   <si>
     <t>Serum chống nắng dưỡng thể hương tươi mát Vaseline Glow Defense SPF50+ PA++++ 260ML/150ML | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/5XqjVBCd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">KEM CHỐNG NẮNG PHỔ RỘNG POND'S UV MIRACLE SPF50+ PA++++ </t>
   </si>
   <si>
     <t>KEM CHỐNG NẮNG PHỔ RỘNG POND'S UV MIRACLE SPF50+ PA++++ | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/8p2pCDm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[MỚI] Sữa chống nắng CeraVe giảm dầu mỏng nhẹ khô thoáng 50ml </t>
   </si>
   <si>
@@ -725,35 +255,12 @@
     <t>[MỚI] Sữa chống nắng CeraVe giảm dầu mỏng nhẹ khô thoáng 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/fYnvTQbM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">|ĐỘC QUYỀN ONLINE| Sữa chống nắng CeraVe mỏng nhẹ dưỡng ẩm đến 24 giờ </t>
   </si>
   <si>
     <t>|ĐỘC QUYỀN ONLINE| Sữa chống nắng CeraVe mỏng nhẹ dưỡng ẩm đến 24 giờ | Shopee Việt Nam</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/fYnvTQbM  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng, mờ nám SVR CLAIRIAL CREME SPF50+ 40ml - DATE T4/2027 </t>
   </si>
   <si>
@@ -763,26 +270,6 @@
     <t>Kem chống nắng, mờ nám SVR CLAIRIAL CREME SPF50+ 40ml - DATE T4/2027 | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/KzwcwqNp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">JMsolution Life Xịt Dưỡng Thể Chống Nắng Nâng Tông Chính hãng Vitamin C Tone Up Skin Protection Spray 150ml </t>
   </si>
   <si>
@@ -792,52 +279,12 @@
     <t>JMsolution Life Xịt Dưỡng Thể Chống Nắng Nâng Tông Chính hãng Vitamin C Tone Up Skin Protection Spray 150ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/6JPcfWRJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">JMsolution Xịt Chống Nắng Dưỡng Ẩm Chiết Xuất Hoa Hồng Glow Luminous Flower Sun Spray Rose 180ml </t>
   </si>
   <si>
     <t>JMsolution Xịt Chống Nắng Dưỡng Ẩm Chiết Xuất Hoa Hồng Glow Luminous Flower Sun Spray Rose 180ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/6R3f11Vz</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tone dưỡng ẩm, làm sáng da Reihaku Hatomugi UV Milky Gel SPF50+ PA++++ (80g)</t>
   </si>
   <si>
@@ -847,205 +294,45 @@
     <t>Kem chống nắng nâng tone dưỡng ẩm, làm sáng da Reihaku Hatomugi UV Milky Gel SPF50+ PA++++ (80g) | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/mVqFbKrQ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Sữa dưỡng thể chống nắng, dưỡng ẩm Hatomugi UV Care &amp; Moisturizing SPF 50+ PA++++ UV Milky Gel 250ml </t>
   </si>
   <si>
     <t>Sữa dưỡng thể chống nắng, dưỡng ẩm Hatomugi UV Care &amp; Moisturizing SPF 50+ PA++++ UV Milky Gel 250ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/nqCG1h7S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Tinh Chất Chống Nắng Nâng Tông SUNCUT Tone Up UV Essence SPF50+ PA++++, Chống Thấm Nước </t>
   </si>
   <si>
     <t>Tinh Chất Chống Nắng Nâng Tông SUNCUT Tone Up UV Essence SPF50+ PA++++, Chống Thấm Nước | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/PZBwgM11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Sữa Dưỡng Thể Chống Nắng Trắng Da Reihaku Hatomugi UV Milky Gel SPF31 PA+++ 250ml Nhật Bản </t>
   </si>
   <si>
     <t>Sữa Dưỡng Thể Chống Nắng Trắng Da Reihaku Hatomugi UV Milky Gel SPF31 PA+++ 250ml Nhật Bản | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/8LGpbd2H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Xịt Chống Nắng Kose Suncut UV Spay Super Water Proof SPF50+ PA++++</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/0ytz8Bz5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Xịt Chống Nắng SUNCUT UV Protect Spray SPF50+ PA++++ Chống Nắng Toàn Diện, Siêu Nhẹ, Không Bết Dính </t>
   </si>
   <si>
     <t>Xịt Chống Nắng SUNCUT UV Protect Spray SPF50+ PA++++ Chống Nắng Toàn Diện, Siêu Nhẹ, Không Bết Dính | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/ymhKBLky</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Sữa Chống Nắng SUNCUT UV Perfect Milk Super Water Proof SPF50+ PA++++ Bảo Vệ Hiệu Qủa ,Chống Nước </t>
   </si>
   <si>
     <t>Sữa Chống Nắng SUNCUT UV Perfect Milk Super Water Proof SPF50+ PA++++ Bảo Vệ Hiệu Qủa ,Chống Nước | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/Pv24XkPh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem Chống Nắng SUNCUT UV Perfect Essence Super Water Proof SPF50+ PA++++ (60g )KOSÉ Cosmeport - 3217 </t>
   </si>
   <si>
     <t>Kem Chống Nắng SUNCUT UV Perfect Essence Super Water Proof SPF50+ PA++++ (60g )KOSÉ Cosmeport - 3217 | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/ymqk0CGh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Torriden Chính hãng] Kem chống nắng nâng tông da Dive-In, 60ml, Sun Cream </t>
   </si>
   <si>
@@ -1055,130 +342,30 @@
     <t>[Torriden Chính hãng] Kem chống nắng nâng tông da Dive-In, 60ml, Sun Cream | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/XxyBTXtS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>[Torriden Chính hãng] Kem chống nắng nâng tông rạng rỡ CELLMAZING, 60ml, Sunscreen</t>
   </si>
   <si>
     <t>[Torriden Chính hãng] Kem chống nắng nâng tông rạng rỡ CELLMAZING, 60ml, Sunscreen | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/TBFFnDhr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Torriden Chính hãng] Kem chống nắng nâng tone da BALANCEFUL CICA với SPF 50+ PA++++, 60ml, Sun Cream </t>
   </si>
   <si>
     <t>[Torriden Chính hãng] Kem chống nắng nâng tone da BALANCEFUL CICA với SPF 50+ PA++++, 60ml, Sun Cream | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/rKmJpbRJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Torriden Chính hãng] Kem chống nắng dưỡng ẩm da DIVE IN chứa Hyaluronic Acid SPF 50+ PA++++, 60ml, Sun Cream </t>
   </si>
   <si>
     <t>[Torriden Chính hãng] Kem chống nắng dưỡng ẩm da DIVE IN chứa Hyaluronic Acid SPF 50+ PA++++, 60ml, Sun Cream | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/dwndYfKt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Torriden Chính hãng] Serum chống nắng cấp ẩm Dive-In Watery Fit, 50ml, Sun Serum </t>
   </si>
   <si>
     <t>[Torriden Chính hãng] Serum chống nắng cấp ẩm Dive-In Watery Fit, 50ml, Sun Serum | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/WvtbKZ5j</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Skin1004 Madagascar Centella Airfit Suncream Plus SPF50+ PA++++ 50ml</t>
   </si>
   <si>
@@ -1188,78 +375,18 @@
     <t>Kem chống nắng Skin1004 Madagascar Centella Airfit Suncream Plus SPF50+ PA++++ 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/Gvp5nN8g</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Tinh chất chống nắng SKIN1004 Centella Hyalu-cica Water-fit Sun Serum SPF50+ PA++++ 50ml </t>
   </si>
   <si>
     <t>Tinh chất chống nắng SKIN1004 Centella Hyalu-cica Water-fit Sun Serum SPF50+ PA++++ 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/d0JjfSRf</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng SKIN1004 Madagascar Centella Poremizing Velvet Finish Sunscreen SPF50+ PA++++ 50ml </t>
   </si>
   <si>
     <t>Kem chống nắng SKIN1004 Madagascar Centella Poremizing Velvet Finish Sunscreen SPF50+ PA++++ 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/bgSC9sjq</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem Chống Nắng PURITO Daily Soft Touch Sunscreen SPF50+ PA++++ 60ml </t>
   </si>
   <si>
@@ -1269,78 +396,18 @@
     <t>Kem Chống Nắng PURITO Daily Soft Touch Sunscreen SPF50+ PA++++ 60ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/qLRXLSMW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Tinh Chất Chống Nắng Rau Má PURITO Wonder Releaf Centella Daily Sun Lotion SPF50+ PA++++ 60ml </t>
   </si>
   <si>
     <t>Tinh Chất Chống Nắng Rau Má PURITO Wonder Releaf Centella Daily Sun Lotion SPF50+ PA++++ 60ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/27cVJd7C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Sáp Chống Nắng PURITO Daily Soft Touch Sun Stick SPF50+ PA++++ 20g </t>
   </si>
   <si>
     <t>Sáp Chống Nắng PURITO Daily Soft Touch Sun Stick SPF50+ PA++++ 20g | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/4nG4dB61</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse lai Vật Lý &amp; Hoá Học Nâng Tone &amp; Hiệu chỉnh da SPF 50+ PA++++ 50ml </t>
   </si>
   <si>
@@ -1350,205 +417,45 @@
     <t>[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse lai Vật Lý &amp; Hoá Học Nâng Tone &amp; Hiệu chỉnh da SPF 50+ PA++++ 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/fYYkcy9D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse lai Vật Lý &amp; Hoá Học Nâng Tone &amp; Hiệu chỉnh da Matte Mịn lì SPF 50+ PA++++ 50mL </t>
   </si>
   <si>
     <t>[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse lai Vật Lý &amp; Hoá Học Nâng Tone &amp; Hiệu chỉnh da Matte Mịn lì SPF 50+ PA++++ 50mL | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/BKP1PYHG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Beplain Chính Hãng] [MỚI] Kem chống nắng vật lý BEPLAIN Sunmuse Skin Beige nâng tone &amp; hiệu chỉnh màu da SPF50+ PA++++ </t>
   </si>
   <si>
     <t>[Beplain Chính Hãng] [MỚI] Kem chống nắng vật lý BEPLAIN Sunmuse Skin Beige nâng tone &amp; hiệu chỉnh màu da SPF50+ PA++++ | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/gbs6Xf45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse Mineral vật lý nâng tone nhẹ nhàng SPF 50+ PA++++ 50ml </t>
   </si>
   <si>
     <t>[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse Mineral vật lý nâng tone nhẹ nhàng SPF 50+ PA++++ 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/tPKmndht</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse lai Vật Lý &amp; Hoá Học, Nâng Tone hồng rạng rỡ và Sáng da SPF 50+ PA++++ 50ml Peach Pink </t>
   </si>
   <si>
     <t>[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse lai Vật Lý &amp; Hoá Học, Nâng Tone hồng rạng rỡ và Sáng da SPF 50+ PA++++ 50ml Peach Pink | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/dJPV7YtZ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse thuần Vật Lý Trà Xanh, Nâng Tone &amp; Che phủ vùng da đỏ SPF 50+ PA++++ 50ml Mild Green</t>
   </si>
   <si>
     <t>[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse thuần Vật Lý Trà Xanh, Nâng Tone &amp; Che phủ vùng da đỏ SPF 50+ PA++++ 50ml Mild Green | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/jkR68hLt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse Hóa Học &amp; Dưỡng Ẩm SPF 50+ PA++++ 50ml </t>
   </si>
   <si>
     <t>[Beplain Chính Hãng] Kem chống nắng BEPLAIN Sunmuse Hóa Học &amp; Dưỡng Ẩm SPF 50+ PA++++ 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/JW7HqbbH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng _x001D_BEPLAIN Sunmuse lai Vật Lý &amp; Hoá Học Nâng Tone &amp; Hiệu chỉnh da Matte Mịn lì SPF 50+ PA++++ 50mL</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/9mn85nNK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[NEW] Dear Klairs Kem chống nắng TXA Supple Tone Up Sun Essence SPF50+ PA++++ 50 ml [FS] </t>
   </si>
   <si>
@@ -1558,52 +465,12 @@
     <t>[NEW] Dear Klairs Kem chống nắng TXA Supple Tone Up Sun Essence SPF50+ PA++++ 50 ml [FS] | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/qMcqvpcK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[NEW] Dear Klairs Kem chống nắng Blue Supple Tone Up Sun Essence SPF50+ PA++++ 50ml [FS] </t>
   </si>
   <si>
     <t>[NEW] Dear Klairs Kem chống nắng Blue Supple Tone Up Sun Essence SPF50+ PA++++ 50ml [FS] | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/VYH8bgTC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Serum chống nắng &amp; ngăn ngừa lão hóa Kiehl’s Dermatologist Solutions Better Screen™ UV Serum 50ml</t>
   </si>
   <si>
@@ -1613,78 +480,18 @@
     <t>Serum chống nắng &amp; ngăn ngừa lão hóa Kiehl’s Dermatologist Solutions Better Screen™ UV Serum 50ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/G3dqhwVc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Kem chống nắng hằng ngày Kiehl's Ultra Light Daily UV Defense SPF 50 PA++++ Anti-pollution 60ml </t>
   </si>
   <si>
     <t>Kem chống nắng hằng ngày Kiehl's Ultra Light Daily UV Defense SPF 50 PA++++ Anti-pollution 60ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/ycWF3fhW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Gel chống nắng Kiehl's Ultra Light Daily UV Defense Aqua Gel SPF 50 PA++++ 60ml </t>
   </si>
   <si>
     <t>Gel chống nắng Kiehl's Ultra Light Daily UV Defense Aqua Gel SPF 50 PA++++ 60ml | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/FbFQkQQR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">DERMAFIRM Kem Lót Trang Điểm Chống Nắng Ultra Soothing Sun Makeup Base R4 50ml (SPF 50+ PA++++) </t>
   </si>
   <si>
@@ -1694,1324 +501,257 @@
     <t>DERMAFIRM Kem Lót Trang Điểm Chống Nắng Ultra Soothing Sun Makeup Base R4 50ml (SPF 50+ PA++++) | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/cchqmG7Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">DERMAFIRM Kem Chống Nắng Toning Soothing Repair R4 40g (SPF 50+ PA++++) </t>
   </si>
   <si>
     <t>DERMAFIRM Kem Chống Nắng Toning Soothing Repair R4 40g (SPF 50+ PA++++) | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/gZt7jntz</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">LABO DERMAFIRM Kem Lót Trang Điểm Chống Nắng Sun Defense 40g (SPF 34+ PA+++) </t>
   </si>
   <si>
     <t>LABO DERMAFIRM Kem Lót Trang Điểm Chống Nắng Sun Defense 40g (SPF 34+ PA+++) | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/0HgHXkp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">[DERMAFIRM CHÍNH THỨC] Đế trang điểm Sun Defense Green 40g </t>
   </si>
   <si>
     <t>[DERMAFIRM CHÍNH THỨC] Đế trang điểm Sun Defense Green 40g | Shopee Việt Nam</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/XrZt22j8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem Chống Nắng Compliment Spf 50+ Chống Tia UVA/UVB cho da mặt và cổ 50ml</t>
   </si>
   <si>
     <t>Compliment No Problem</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/99BrsJbV</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem Chống Nắng Ngăn Ngừa Mụn Decumar 50g, Kiềm Dầu, Thẩm Thấu Nhanh, SPF 50+, PA++++</t>
   </si>
   <si>
     <t>Decumar</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/WWWyp1F7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng sáng da kiềm dầu cho da mụn, nâng tone Suncream Decumar THC SPF 50+ PA+++ chính hãng, chống trôi</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/WWWyp1F </t>
-  </si>
-  <si>
     <t>Kem chống nắng kiềm dầu &amp; ngừa mụn Eucerin Sun Dry Touch SPF50+ 50ml | Skincare</t>
   </si>
   <si>
     <t>Eucerin</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/PZnvVt4r</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng cho da nhạy cảm Eucerin Hydro Ultra Light SPF 50+ 50ml | Skincare</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/PZnvVt4 </t>
-  </si>
-  <si>
     <t>Kem chống nắng bảo vệ da mỏng nhẹ không bết dính SPF 50+ UVA &amp; UVB Vichy Capital Soleil Dry Touch</t>
   </si>
   <si>
     <t>Vichy</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/zVfRYnpw</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng giảm thâm nám SPF50 Vichy Capital Soleil UVB+UVA Anti DarkSpot 3in1 50ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/nscsbPRg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng bảo vệ, giảm lão hóa Vichy Capital Soleil 3in1 Anti-Aging SPF50 50ml</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/nscsbPR </t>
-  </si>
-  <si>
     <t>[CHỐNG NẮNG WATERGEL MỚI] Chống Nắng Phổ Rộng Thoáng Da, Kháng Mọi Tác Động UV Defender SPF 50+ PA++++ Loreal</t>
   </si>
   <si>
     <t>L’Oréal</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/B5r3pN7d</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Sữa chống nắng phổ rộng mỏng nhẹ bảo vệ da và dưỡng sáng mờ thâm nám Glycolic Bright Anti-Dark Spot L’Oréal Paris 50ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/XfPyfRV4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng dưỡng trắng, kiểm dầu dùng mỗi ngày dạng sữa Sunplay Skin Aqua Clear White Eco Việt Nam SPF50, PA++++ 55g</t>
   </si>
   <si>
     <t>Sunplay</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/BV0Tj5Ny</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Skin Aqua dưỡng ẩm, dạng sữa dùng hàng ngày Sunplay Skin UV Moisture SPF 50, PA++++ 30g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/WpzFmw8D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Sunplay cực mạnh, ngừa đen sạm da hiệu quả dạng sữa Sunplay Super Block SPF 50+, PA++++ 70g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/7N4YPWm9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng vật lý kiềm dầu dạng sữa dùng mỗi ngày Sunplay Skin Aqua Mineral Defense Oil Clear Milk SPF50+ PA++++ 25g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/rfw7r2Lp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Skin Aqua cho da mụn,dạng sữa dùng hàng ngày Sunplay Skin Aqua Acne Clear Eco Việt Nam SPF 50,PA++++ 25g</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/rfw7r2L </t>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tông cho da tối màu &amp; da vàng, dạng sữa Sunplay Skin Aqua Tone Up UV Milk Lavender SPF 50+ PA++++50g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/hxLZv94t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tông cho da vàng, khuyết điểm đỏ, dạng sữa Sunplay Skin Aqua Tone Up UV Milk Blue SPF 50+ PA++++</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/Y7qGYcxQ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng dưỡng da chuyên sâu dạng serum Skin Aqua UV Defense Duo Serum 30g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/sd1td8qG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Sunplay dưỡng trắng da, dạng sữa Sunplay Whitening UV SPF 50, PA++++ 30g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/ZzRGMXqT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Sunplay mát lạnh giải nhiệt dạng sữa Sunplay Super Cool SPF 50, PA++++ 30g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/rfsCkR5Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng trang điểm tạo nền trắng mịn &amp; đều màu dạng sữa Sunplay Skin Clear White CC Milk SPF 50, PA++++ 25g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/nstMZkp9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng dưỡng trắng &amp; dưỡng ẩm, dùng mỗi ngày Sunplay Skin Aqua Silky White Eco Việt Nam SPF 50, PA++++ 30g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/B2fdB3pm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tông da tái xanh dạng sữa Sunplay Skin Aqua Tone Up UV Milk Rose SPF 50+ PA++++ 50g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/B2pd6kX8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tông cho da có khuyết điểm dạng sữa Sunplay Skin Aqua Tone Up UV Milk Mint Green SPF 50+ PA++++ 50g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/6QgwDq6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tông mọi tông da dạng sữa Sunplay Skin Aqua Tone Up UV Milk Latte Beige SPF 50+ PA++++ 50g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/bRvB1pLs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Serum chống nắng ngăn sạm,nám da Skin Aqua Nexta Shield Serum UV Essence SPF50+ PA++++ 50g (dạng tinh chất)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/kg6xRWDJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Sunplay cho bé từ 6 tháng tuổi và da nhạy cảm, dạng sữa Sunplay Baby Mild SPF 35, PA++ 30g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/C3ZfWmxX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Gel chống nắng dưỡng sáng nâng tông &amp; hiệu chỉnh sắc da Anessa SPF50+ PA++++ 40g</t>
   </si>
   <si>
     <t>Anessa</t>
   </si>
   <si>
-    <t>https://ibb.co/BVhCcyMx</t>
-  </si>
-  <si>
     <t>Sữa chống nắng dưỡng da kiềm dầu bảo vệ hoàn hảo Anessa Gold Milk SPF50+ PA++++ 20ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/MxTfqxFj</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Sữa chống nắng dưỡng da dịu nhẹ an toàn cho da nhạy cảm và trẻ em Anessa Mild Milk SPF50+ PA++++ 60ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/3yTk27xb</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Xịt chống nắng dưỡng da đa năng tiện dụng bảo vệ hoàn hảo Anessa Gold Spray SPF50+ PA++++ 60g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/vxrtjLNd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Gel chống nắng dưỡng da 24H cân bằng độ ẩm Anessa Moisture UV Gel SPF50+ PA++++ 90g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/m5qgGcZr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Gel chống nắng cho bé, công thức thuần vật lý an toàn cho da nhạy cảm và trẻ em Anessa Mild Gel SPF35 PA+++ 90g</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/0p4mdFht</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Serum Chống Nắng Dưỡng Da Nâng Tông Anessa Day Serum SPF50+ PA++++ 30ml</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ibb.co/0p4mdFht  </t>
-  </si>
-  <si>
     <t>Kem chống nắng dưỡng ẩm 2in1 cho da thiên dầu nhạy cảm Cetaphil Daily Defense Cream SPF50 50G</t>
   </si>
   <si>
     <t>Centaphil</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/N6q0Cd9q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Gel chống nắng vật lý dưỡng ẩm 2in1 dịu lành cho da thiên khô nhạy cảm Cetaphil Sun SPF 50+ Light Gel 50ML</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/1GrmGtQn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem Chống Nắng Hằng Ngày Dưỡng Sáng Sa Sulwhasoo UV Daily Sunscreen 50ml</t>
   </si>
   <si>
     <t xml:space="preserve"> Sulwhasoo</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/V0YJQyhH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Sữa Chống Nắng Kiềm Dầu Kháng Nước Sulwhasoo UV Daily Fluid Sunscreen 50ML</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/WvnbmXk8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tone Tím d'Alba White Truffle Tone Up Sunscreen (Purple) 50ml</t>
   </si>
   <si>
     <t>d’ Alba</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/G3nHn4ZX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tone Hồng Waterfull Tone-up Sun Cream 50ml</t>
   </si>
   <si>
-    <t>https://ibb.co/1G5YXCj1</t>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tone Cover Beige 50ml Suncream Foundation-Free Cover-Up Cream (SPF50 + PA ++++)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/JwPHczk3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng vật lý dịu nhẹ cho da nhạy cảm Waterfull Mild Suncream SPF 50+ 50ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/TxXNDxsq</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng d'Alba nâng da Tone Waterfull Tone-up Sun Cream SPF 50 + 50ml</t>
   </si>
   <si>
-    <t>https://ibb.co/HDWp55cT</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Kem chống nắng Nâng tone Xanh lá White Truffle Tone Up Green Correcting Suncream 50ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/rGW2XgpS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve"> Xịt chống nắng Làm mát tức thì Chống nắng tối ưu SPF 50+ PA ++++ 50ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/67fch36t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Sữa chống nắng 3 trong 1 chứa Panthenol mỏng nhẹ cấp nước Waterfull Panthenol Liquid Essence Sun Serum 50ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/Y4h9Kck1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem Chống Nắng CARYOPHY 50ml (CARYOPHY Smart Tone-up Sunscreen)</t>
   </si>
   <si>
     <t>Carophy</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/Rkz7Lm5x</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem Chống Nắng Dr.Pepti Uv Plus Moist-up Sunscreen SPF 50+ PA++++ Phổ Rộng, Làm Mát, Bảo Vệ Da 50ml CN05</t>
   </si>
   <si>
     <t>Dr.pepti</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/5XN9P9DG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem Chống Nắng Nâng Tone Dr.PEPTI 50ml SPF 50+ PA++++ Dưỡng Trắng, Kiềm Dầu Cho Mọi Loại Da</t>
   </si>
   <si>
-    <t>https://ibb.co/C3MSFnS4</t>
-  </si>
-  <si>
     <t>Kem chống nắng Neutrogena® Ultra Sheer Fluid Sunscreen Age Shield SPF 50 Broad Spectrum PA++++ 40ml</t>
   </si>
   <si>
     <t>Neutrogena</t>
   </si>
   <si>
-    <t>https://ibb.co/gZRJN9fc</t>
-  </si>
-  <si>
     <t>Kem chống nắng Neutrogena® U.S Dry Touch SPF 50 (88ml)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/d0Sy1Syh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng Neutrogena Ultra Sheer Age Shield 40ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/6RnrwfXz</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng phổ rộng dưỡng ẩm cho da khô Embryolisse Crème Solaire 100ml</t>
   </si>
   <si>
     <t>EMBRYOLISSE</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/Rpc6j46j</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Sữa chống nắng Curel UV Protection Milk SPF 50+ PA+++ 60ml</t>
   </si>
   <si>
     <t>Curél</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/kgMBxZTq</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng nâng tông Dr.G Brightening Up Sun+ DrG 50ml</t>
   </si>
   <si>
     <t>Dr.G</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/PvZgbtJ7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng vật lý Dr.G Green Mild Up Sun+ DrG 50ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/My4gvXCC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Kem chống nắng hóa học Dr.G R.E.D Blemish DrG 50ml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/wFKbwHK2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Chống nắng dạng thỏi Dr.G Mild Up Sun Stick DrG</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://ibb.co/svzb40dd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>https://s.shpee.vn/zm2i1j</t>
+  </si>
+  <si>
+    <t>Link ảnh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3025,13 +765,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -3043,19 +776,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -3082,12 +803,6 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -3107,7 +822,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -3196,77 +911,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3496,7 +1231,6 @@
     <col min="1" max="1" width="117.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
     <col min="3" max="3" width="171.140625" customWidth="1"/>
-    <col min="4" max="4" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3506,1649 +1240,1389 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>3</v>
+      <c r="D1" s="24" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>7</v>
-      </c>
+      <c r="D2" s="24"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>10</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="24"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>13</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="24"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>16</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="24"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>19</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="24"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>22</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>26</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="24"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>29</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B9" s="15"/>
+      <c r="C9" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>32</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="24"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>36</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="24"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>39</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="24"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>42</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="24"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>45</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="24"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>48</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="24"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>52</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="24"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>55</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="24"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>58</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B18" s="15"/>
+      <c r="C18" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="24"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>61</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="24"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>64</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B20" s="15"/>
+      <c r="C20" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>67</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>71</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="24"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>74</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>78</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="24"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>81</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="24"/>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>85</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="24"/>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>88</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="24"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>91</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="24"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>95</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="24"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="24"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>101</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="24"/>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>104</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="24"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="4" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>108</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="24"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>111</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="24"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="4" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>115</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="24"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>119</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="24"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>122</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="24"/>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="4" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>126</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" s="24"/>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>129</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="24"/>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>132</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="24"/>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>135</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" s="24"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>137</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" s="24"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>140</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B43" s="15"/>
+      <c r="C43" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" s="24"/>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>143</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" s="24"/>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>146</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B45" s="17"/>
+      <c r="C45" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="24"/>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="4" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>150</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="24"/>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>153</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="24"/>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>156</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="24"/>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>159</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" s="24"/>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>162</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" s="24"/>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="4" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>166</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D51" s="24"/>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>169</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" s="24"/>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>172</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B53" s="17"/>
+      <c r="C53" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" s="24"/>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="4" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>176</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" s="24"/>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>179</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" s="24"/>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>182</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="B56" s="17"/>
+      <c r="C56" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" s="24"/>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="4" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>186</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D57" s="24"/>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>189</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D58" s="24"/>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>192</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D59" s="24"/>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>195</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B60" s="15"/>
+      <c r="C60" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D60" s="24"/>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>198</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D61" s="24"/>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>201</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D62" s="24"/>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>204</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D63" s="24"/>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B64" s="18"/>
-      <c r="C64" s="25" t="s">
-        <v>369</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>206</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="B64" s="17"/>
+      <c r="C64" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="D64" s="24"/>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="C65" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>210</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D65" s="24"/>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B66" s="20"/>
-      <c r="C66" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>213</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" s="24"/>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="4" t="s">
-        <v>214</v>
+        <v>148</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="C67" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>217</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D67" s="24"/>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>220</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D68" s="24"/>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B69" s="18"/>
-      <c r="C69" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>223</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="B69" s="17"/>
+      <c r="C69" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="D69" s="24"/>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="4" t="s">
-        <v>224</v>
+        <v>155</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="C70" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>227</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D70" s="24"/>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>230</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" s="24"/>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>233</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D72" s="24"/>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B73" s="18"/>
-      <c r="C73" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>236</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="B73" s="17"/>
+      <c r="C73" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="D73" s="24"/>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="4" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>239</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="D74" s="24"/>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="4" t="s">
-        <v>240</v>
+        <v>166</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>242</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="D75" s="24"/>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>244</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B76" s="17"/>
+      <c r="C76" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="D76" s="24"/>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="4" t="s">
-        <v>245</v>
+        <v>169</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="C77" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>247</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C77" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="D77" s="24"/>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B78" s="18"/>
-      <c r="C78" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>249</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="B78" s="17"/>
+      <c r="C78" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="D78" s="24"/>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="4" t="s">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="C79" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="D79" s="14" t="s">
-        <v>252</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="C79" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D79" s="24"/>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>254</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="B80" s="15"/>
+      <c r="C80" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D80" s="24"/>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B81" s="18"/>
-      <c r="C81" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="D81" s="15" t="s">
-        <v>256</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="B81" s="17"/>
+      <c r="C81" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="D81" s="24"/>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>176</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="D82" s="14" t="s">
-        <v>259</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="C82" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="D82" s="24"/>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="4" t="s">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="B83" s="8"/>
-      <c r="C83" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>261</v>
-      </c>
+      <c r="C83" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="D83" s="24"/>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>179</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C84" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="D84" s="14" t="s">
-        <v>264</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="C84" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D84" s="24"/>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="4" t="s">
-        <v>265</v>
+        <v>181</v>
       </c>
       <c r="B85" s="9"/>
-      <c r="C85" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>266</v>
-      </c>
+      <c r="C85" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="D85" s="24"/>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>182</v>
       </c>
       <c r="B86" s="9"/>
-      <c r="C86" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>268</v>
-      </c>
+      <c r="C86" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D86" s="24"/>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="4" t="s">
-        <v>269</v>
+        <v>183</v>
       </c>
       <c r="B87" s="9"/>
-      <c r="C87" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>270</v>
-      </c>
+      <c r="C87" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D87" s="24"/>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>184</v>
       </c>
       <c r="B88" s="9"/>
-      <c r="C88" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>272</v>
-      </c>
+      <c r="C88" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="D88" s="24"/>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="4" t="s">
-        <v>273</v>
+        <v>185</v>
       </c>
       <c r="B89" s="9"/>
-      <c r="C89" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>274</v>
-      </c>
+      <c r="C89" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="D89" s="24"/>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="4" t="s">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="B90" s="9"/>
-      <c r="C90" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>276</v>
-      </c>
+      <c r="C90" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D90" s="24"/>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="4" t="s">
-        <v>277</v>
+        <v>187</v>
       </c>
       <c r="B91" s="9"/>
-      <c r="C91" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>278</v>
-      </c>
+      <c r="C91" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="D91" s="24"/>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="4" t="s">
-        <v>279</v>
+        <v>188</v>
       </c>
       <c r="B92" s="9"/>
-      <c r="C92" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>280</v>
-      </c>
+      <c r="C92" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D92" s="24"/>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="4" t="s">
-        <v>281</v>
+        <v>189</v>
       </c>
       <c r="B93" s="9"/>
-      <c r="C93" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>282</v>
-      </c>
+      <c r="C93" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="D93" s="24"/>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>190</v>
       </c>
       <c r="B94" s="9"/>
-      <c r="C94" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>284</v>
-      </c>
+      <c r="C94" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D94" s="24"/>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="4" t="s">
-        <v>285</v>
+        <v>191</v>
       </c>
       <c r="B95" s="9"/>
-      <c r="C95" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>286</v>
-      </c>
+      <c r="C95" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="D95" s="24"/>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="B96" s="9"/>
-      <c r="C96" s="24" t="s">
-        <v>287</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>288</v>
-      </c>
+      <c r="C96" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" s="24"/>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="4" t="s">
-        <v>289</v>
+        <v>193</v>
       </c>
       <c r="B97" s="9"/>
-      <c r="C97" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="D97" s="14" t="s">
-        <v>290</v>
-      </c>
+      <c r="C97" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D97" s="24"/>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>194</v>
       </c>
       <c r="B98" s="9"/>
-      <c r="C98" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>292</v>
-      </c>
+      <c r="C98" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D98" s="24"/>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="4" t="s">
-        <v>293</v>
+        <v>195</v>
       </c>
       <c r="B99" s="9"/>
-      <c r="C99" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>294</v>
-      </c>
+      <c r="C99" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D99" s="24"/>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="B100" s="10"/>
-      <c r="C100" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>296</v>
-      </c>
+      <c r="C100" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D100" s="24"/>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="4" t="s">
-        <v>297</v>
+        <v>197</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C101" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="D101" s="14" t="s">
-        <v>299</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C101" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="D101" s="24"/>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B102" s="17"/>
-      <c r="C102" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>301</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D102" s="24"/>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B103" s="17"/>
-      <c r="C103" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>303</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D103" s="24"/>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B104" s="17"/>
-      <c r="C104" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="D104" s="14" t="s">
-        <v>305</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="B104" s="15"/>
+      <c r="C104" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="D104" s="24"/>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B105" s="17"/>
-      <c r="C105" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="D105" s="14" t="s">
-        <v>307</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="D105" s="24"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B106" s="17"/>
-      <c r="C106" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="D106" s="14" t="s">
-        <v>309</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="D106" s="24"/>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B107" s="18"/>
-      <c r="C107" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="D107" s="15" t="s">
-        <v>311</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="B107" s="17"/>
+      <c r="C107" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="D107" s="24"/>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>205</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="C108" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>314</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C108" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="D108" s="24"/>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B109" s="18"/>
-      <c r="C109" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="D109" s="14" t="s">
-        <v>316</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="B109" s="17"/>
+      <c r="C109" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="D109" s="24"/>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>208</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="C110" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="D110" s="14" t="s">
-        <v>319</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C110" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="D110" s="24"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B111" s="18"/>
-      <c r="C111" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="D111" s="14" t="s">
-        <v>321</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="B111" s="17"/>
+      <c r="C111" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="D111" s="24"/>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="4" t="s">
-        <v>322</v>
+        <v>211</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="C112" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="D112" s="14" t="s">
-        <v>324</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C112" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D112" s="24"/>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B113" s="17"/>
-      <c r="C113" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="D113" s="15" t="s">
-        <v>326</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="D113" s="24"/>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B114" s="17"/>
-      <c r="C114" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="D114" s="14" t="s">
-        <v>328</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="B114" s="15"/>
+      <c r="C114" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="D114" s="24"/>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B115" s="17"/>
-      <c r="C115" s="24" t="s">
-        <v>329</v>
-      </c>
-      <c r="D115" s="14" t="s">
-        <v>330</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="D115" s="24"/>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B116" s="17"/>
-      <c r="C116" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="D116" s="14" t="s">
-        <v>332</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="B116" s="15"/>
+      <c r="C116" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="D116" s="24"/>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B117" s="17"/>
-      <c r="C117" s="24" t="s">
-        <v>333</v>
-      </c>
-      <c r="D117" s="14" t="s">
-        <v>334</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D117" s="24"/>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B118" s="17"/>
-      <c r="C118" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="D118" s="14" t="s">
-        <v>336</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="B118" s="15"/>
+      <c r="C118" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="D118" s="24"/>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B119" s="17"/>
-      <c r="C119" s="24" t="s">
-        <v>337</v>
-      </c>
-      <c r="D119" s="14" t="s">
-        <v>338</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="B119" s="15"/>
+      <c r="C119" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D119" s="24"/>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="11" t="s">
-        <v>339</v>
+        <v>220</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="C120" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="D120" s="14" t="s">
-        <v>341</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C120" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="D120" s="24"/>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="4" t="s">
-        <v>342</v>
+        <v>222</v>
       </c>
       <c r="B121" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="C121" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="D121" s="14" t="s">
-        <v>344</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C121" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="D121" s="24"/>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B122" s="18"/>
-      <c r="C122" s="24" t="s">
-        <v>345</v>
-      </c>
-      <c r="D122" s="14" t="s">
-        <v>346</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="B122" s="17"/>
+      <c r="C122" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D122" s="24"/>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="4" t="s">
-        <v>347</v>
+        <v>225</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="C123" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="D123" s="14" t="s">
-        <v>349</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C123" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D123" s="24"/>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B124" s="17"/>
-      <c r="C124" s="24" t="s">
-        <v>350</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>351</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="B124" s="15"/>
+      <c r="C124" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="D124" s="24"/>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B125" s="18"/>
-      <c r="C125" s="24" t="s">
-        <v>352</v>
-      </c>
-      <c r="D125" s="14" t="s">
-        <v>353</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="B125" s="17"/>
+      <c r="C125" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D125" s="24"/>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="4" t="s">
-        <v>354</v>
+        <v>229</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="C126" s="24" t="s">
-        <v>354</v>
-      </c>
-      <c r="D126" s="14" t="s">
-        <v>356</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C126" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="D126" s="24"/>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="4" t="s">
-        <v>357</v>
+        <v>231</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C127" s="24" t="s">
-        <v>357</v>
-      </c>
-      <c r="D127" s="14" t="s">
-        <v>359</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C127" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="D127" s="24"/>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="4" t="s">
-        <v>360</v>
+        <v>233</v>
       </c>
       <c r="B128" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C128" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="D128" s="14" t="s">
-        <v>362</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C128" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="D128" s="24"/>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="B129" s="17"/>
-      <c r="C129" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="D129" s="14" t="s">
-        <v>364</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="B129" s="15"/>
+      <c r="C129" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="D129" s="24"/>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="B130" s="17"/>
-      <c r="C130" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="D130" s="14" t="s">
-        <v>366</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="B130" s="15"/>
+      <c r="C130" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="D130" s="24"/>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B131" s="18"/>
-      <c r="C131" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="D131" s="14" t="s">
-        <v>368</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="B131" s="17"/>
+      <c r="C131" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="D131" s="24"/>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
-      <c r="C132" s="26"/>
+      <c r="C132" s="13"/>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="12"/>
@@ -9272,17 +6746,11 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B45"/>
+    <mergeCell ref="B128:B131"/>
+    <mergeCell ref="B123:B125"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B112:B119"/>
+    <mergeCell ref="B110:B111"/>
     <mergeCell ref="B46:B50"/>
     <mergeCell ref="B51:B53"/>
     <mergeCell ref="B54:B56"/>
@@ -9295,273 +6763,149 @@
     <mergeCell ref="B57:B64"/>
     <mergeCell ref="B65:B66"/>
     <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B128:B131"/>
-    <mergeCell ref="B123:B125"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B112:B119"/>
-    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B45"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B11:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D5" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D6" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="D7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="C8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D8" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="D9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C10" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="D10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C11" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="D11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C12" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="D12" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C13" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="D13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C14" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="D14" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C15" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D15" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C16" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="D16" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C17" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="D17" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C18" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="D18" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C19" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="D19" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C20" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="D20" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C21" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="D21" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C22" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="D22" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C23" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="D23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C24" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="D24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C25" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="D25" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C26" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="D26" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C27" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D27" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C28" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="D28" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C29" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="D29" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C30" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="D30" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C31" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D31" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C32" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D32" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C33" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D33" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C34" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D34" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C35" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D35" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C36" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D36" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C37" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D37" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C38" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D38" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C39" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D39" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C40" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D40" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C41" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D41" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C42" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D42" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C43" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D43" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C44" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D44" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C45" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D45" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C46" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D46" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C47" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D47" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C48" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D48" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C49" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D49" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C50" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D50" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C51" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D51" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="C52" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D52" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="C53" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D53" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="C54" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D54" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="C55" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D55" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="C56" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D56" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="C57" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D57" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="C58" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D58" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="C59" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D59" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="C60" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D60" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="C61" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D61" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="C62" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D62" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="C63" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D63" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="C64" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D64" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="C65" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D65" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="C66" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D66" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="C67" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D67" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C68" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D68" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C69" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D69" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C70" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D70" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C71" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D71" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C72" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D72" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C73" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D73" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C74" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D74" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C75" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D75" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C76" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D76" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C77" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D77" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C78" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D78" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C79" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D79" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C80" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D80" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C81" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D81" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C82" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D82" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C83" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D83" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C84" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D84" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C85" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D85" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="C86" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D86" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C87" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D87" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C88" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D88" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C89" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D89" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C90" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D90" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C91" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D91" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C92" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D92" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C93" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D93" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C94" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D94" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C95" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D95" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C96" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D96" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C97" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D97" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C98" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D98" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C99" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D99" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C100" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D100" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C101" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D101" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C102" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D102" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C103" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D103" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C104" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D104" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C105" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="D105" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C106" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="D106" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C107" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="D107" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C108" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="D108" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C109" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="D109" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C110" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="D110" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="C111" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="D111" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C112" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="D112" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C113" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="D113" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C114" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="D114" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C115" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="D115" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C116" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="D116" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C117" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="D117" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C118" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="D118" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C119" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="D119" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="C120" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="D120" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="C121" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="D121" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="C122" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="D122" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="C123" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="D123" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="C124" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="D124" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="C125" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="D125" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="C126" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="D126" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="C127" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="D127" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="C128" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="D128" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="C129" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="D129" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="C130" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="D130" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="C131" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="D131" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="C33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="C56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="C63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="C64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="C66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="C70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="C71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="C105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="C112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="C121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="C122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="C123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="C124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="C125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="C126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="C127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="C128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="C129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="C130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="C131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
